--- a/data-raw/SAA.xlsx
+++ b/data-raw/SAA.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11114"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11211"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sebsilas/MST/data-raw/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sebsilas/SAA/data-raw/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DFB6E13D-9FB0-D448-ADF9-9FBECA5AA36B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A64825A3-D437-2347-BA27-260D9603B20C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="1060" windowWidth="35840" windowHeight="19200" xr2:uid="{F918617E-B214-614F-96D8-792A3F23E788}"/>
+    <workbookView xWindow="1280" yWindow="2060" windowWidth="35840" windowHeight="19200" xr2:uid="{F918617E-B214-614F-96D8-792A3F23E788}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -44,9 +44,6 @@
     <t>en</t>
   </si>
   <si>
-    <t>Welcome to the Melody Singing Task!</t>
-  </si>
-  <si>
     <t>When you click the Play button in the next set of trials, you will hear a 5-second note</t>
   </si>
   <si>
@@ -62,18 +59,12 @@
     <t>How to Sing</t>
   </si>
   <si>
-    <t>mst_welcome</t>
-  </si>
-  <si>
     <t>long_tone_instruction</t>
   </si>
   <si>
     <t>long_tone_instruction_2</t>
   </si>
   <si>
-    <t>mst_button_play_note_and_sing</t>
-  </si>
-  <si>
     <t>After hearing the melody, do your best to sing it back, then click Stop. You can try each melody up to 3 times. It's okay if you don't think you got it, just try your best!</t>
   </si>
   <si>
@@ -86,30 +77,9 @@
     <t>sing_melody_trial_instructions3</t>
   </si>
   <si>
-    <t>mst_welcome_1</t>
-  </si>
-  <si>
-    <t>mst_welcome_2</t>
-  </si>
-  <si>
-    <t>mst_instructions1</t>
-  </si>
-  <si>
-    <t>mst_instructions2</t>
-  </si>
-  <si>
-    <t>mst_instructions3</t>
-  </si>
-  <si>
-    <t>mst_instructions4</t>
-  </si>
-  <si>
     <t>task_name</t>
   </si>
   <si>
-    <t>Melody Singing Task</t>
-  </si>
-  <si>
     <t>Please read the instructions carefully.</t>
   </si>
   <si>
@@ -123,6 +93,36 @@
   </si>
   <si>
     <t>In this task we’ll ask you to sing back a few notes and melodies that we play to you. It is fine if you think you are not a good singer. Throughout this first singing test, you will probably find some examples easy and others harder, and in general, as this specific singing test progresses, the trials become more challenging. Just always make your best attempt.</t>
+  </si>
+  <si>
+    <t>Welcome to the Singing Ability Assessment!</t>
+  </si>
+  <si>
+    <t>Singing Ability Assessment</t>
+  </si>
+  <si>
+    <t>SAA_welcome</t>
+  </si>
+  <si>
+    <t>SAA_welcome_1</t>
+  </si>
+  <si>
+    <t>SAA_welcome_2</t>
+  </si>
+  <si>
+    <t>SAA_instructions1</t>
+  </si>
+  <si>
+    <t>SAA_instructions2</t>
+  </si>
+  <si>
+    <t>SAA_instructions3</t>
+  </si>
+  <si>
+    <t>SAA_instructions4</t>
+  </si>
+  <si>
+    <t>SAA_button_play_note_and_sing</t>
   </si>
 </sst>
 </file>
@@ -548,79 +548,79 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A2" s="5" t="s">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>3</v>
+        <v>20</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A3" s="8" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="B3" s="9" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A4" s="8" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A5" s="8" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A6" s="8" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>27</v>
+        <v>17</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A7" s="8" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A8" s="8" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A9" s="10" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A10" s="10" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A11" s="10" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="B11" s="8" t="s">
         <v>0</v>
@@ -628,34 +628,34 @@
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A12" s="10" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A13" s="10" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A14" s="10" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A15" s="10" t="s">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.2">

--- a/data-raw/SAA.xlsx
+++ b/data-raw/SAA.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11211"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10111"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sebsilas/SAA/data-raw/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sebsilas/Downloads/retranslations/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A64825A3-D437-2347-BA27-260D9603B20C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{715ECFD8-67F5-EA49-8B74-C48B9B7643A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1280" yWindow="2060" windowWidth="35840" windowHeight="19200" xr2:uid="{F918617E-B214-614F-96D8-792A3F23E788}"/>
+    <workbookView xWindow="220" yWindow="1260" windowWidth="28800" windowHeight="17540" xr2:uid="{F918617E-B214-614F-96D8-792A3F23E788}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="38">
   <si>
     <t>Play Note and Sing Along</t>
   </si>
@@ -44,27 +44,12 @@
     <t>en</t>
   </si>
   <si>
-    <t>When you click the Play button in the next set of trials, you will hear a 5-second note</t>
-  </si>
-  <si>
-    <t>Please try and sing the exact same note and hold.</t>
-  </si>
-  <si>
     <t>Sing A Melody You Hear</t>
   </si>
   <si>
-    <t>On this set of trials, you will click  to hear a melody.</t>
-  </si>
-  <si>
     <t>How to Sing</t>
   </si>
   <si>
-    <t>long_tone_instruction</t>
-  </si>
-  <si>
-    <t>long_tone_instruction_2</t>
-  </si>
-  <si>
     <t>After hearing the melody, do your best to sing it back, then click Stop. You can try each melody up to 3 times. It's okay if you don't think you got it, just try your best!</t>
   </si>
   <si>
@@ -89,9 +74,6 @@
     <t>You will be asked to imitate some sounds.  Please sing these notes back on the syllable "daah"   as in  the first part of the word  “dog” [rhymes with “fa la la”. ].</t>
   </si>
   <si>
-    <t xml:space="preserve"> Try to produce notes that are as stable as possible, without vibrato. That is, try note to wobble  your notes.  The computer can analyse a “straight” sound best. </t>
-  </si>
-  <si>
     <t>In this task we’ll ask you to sing back a few notes and melodies that we play to you. It is fine if you think you are not a good singer. Throughout this first singing test, you will probably find some examples easy and others harder, and in general, as this specific singing test progresses, the trials become more challenging. Just always make your best attempt.</t>
   </si>
   <si>
@@ -123,6 +105,48 @@
   </si>
   <si>
     <t>SAA_button_play_note_and_sing</t>
+  </si>
+  <si>
+    <t>de</t>
+  </si>
+  <si>
+    <t>Willkommen zum Singing Ability Assessment!</t>
+  </si>
+  <si>
+    <t>In diesem Test bitten wir Sie ein paar Töne und Melodien nachzusingen, die wir Ihnen vorspielen. Es ist ok wenn Sie glauben, kein guter Sänger zu sein. Während des ersten Gesangstestes werden Sie wahrscheinlich einige Aufgaben leicht finden und andere schwieriger. Generell werden die Aufgaben über den Verlauf dieses speziellen Gesangstestes mehr und mehr herausfordernd. Geben Sie einfach immer Ihr Bestes.</t>
+  </si>
+  <si>
+    <t>Bitte lesen Sie aufmerksam die Anweisungen.</t>
+  </si>
+  <si>
+    <t>Sie werden gebeten werden einige Töne nachzuahmen. Bitte singen Sie diese Noten auf der Sylbe "daah" nach, so wie am Anfang des Names "David".</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Try to produce notes that are as stable as possible, without vibrato. That is, try not to wobble your notes. The computer can analyse a “straight” sound best. </t>
+  </si>
+  <si>
+    <t>Versuchen Sie Töne zu produzieren, die so stabil wie möglich sind, ohne Vibrato. Das bedeutet, versuchen Sie Ihre Töne nicht flattern zu lassen. Der Computer can einen "klaren" Ton besser analysieren.</t>
+  </si>
+  <si>
+    <t>Singen Sie direkt in Ihr Mikrofon, nicht zu weit davon weg, ungefähr die Distanz eines 30cm langen Lineals.</t>
+  </si>
+  <si>
+    <t>Ton Abspielen und Mitsingen</t>
+  </si>
+  <si>
+    <t>On this set of trials, you will click to hear a melody.</t>
+  </si>
+  <si>
+    <t>Bei dieser Gruppe von Aufgaben werden Sie klicken um eine Melodie zu hören.</t>
+  </si>
+  <si>
+    <t>Singen Sie eine Melodie, die sie hören</t>
+  </si>
+  <si>
+    <t>Nachdem Sie die Melodie gehört haben, versuchen Sie diese bestmöglich nachzusingen. Dann klicken Sie auf Stop. Sie können jede Melodie bis zu dreimal versuchen. Es ist okay wenn Sie denken, dass Sie das nicht ganz geschafft haben. Versuchen Sie einfach Ihr Bestes!</t>
+  </si>
+  <si>
+    <t>Wie Sie Singen sollten</t>
   </si>
 </sst>
 </file>
@@ -525,7 +549,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5BF35A9C-231E-5348-9328-9A574E33D2C7}">
-  <dimension ref="A1:E52"/>
+  <dimension ref="A1:E50"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="35.1640625" style="2" customWidth="1"/>
@@ -542,121 +566,153 @@
       <c r="B1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="1"/>
+      <c r="C1" s="1" t="s">
+        <v>24</v>
+      </c>
       <c r="D1" s="1"/>
       <c r="E1" s="1"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A2" s="5" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>20</v>
+        <v>14</v>
+      </c>
+      <c r="C2" s="6" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A3" s="8" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="B3" s="9" t="s">
-        <v>19</v>
+        <v>13</v>
+      </c>
+      <c r="C3" s="9" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A4" s="8" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>15</v>
+        <v>10</v>
+      </c>
+      <c r="C4" s="9" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A5" s="8" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>7</v>
+        <v>4</v>
+      </c>
+      <c r="C5" s="9" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A6" s="8" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>17</v>
+        <v>12</v>
+      </c>
+      <c r="C6" s="9" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A7" s="8" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>18</v>
+        <v>29</v>
+      </c>
+      <c r="C7" s="9" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A8" s="8" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>16</v>
+        <v>11</v>
+      </c>
+      <c r="C8" s="9" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A9" s="10" t="s">
-        <v>8</v>
-      </c>
-      <c r="B9" s="9" t="s">
-        <v>3</v>
+        <v>23</v>
+      </c>
+      <c r="B9" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="C9" s="8" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A10" s="10" t="s">
-        <v>9</v>
-      </c>
-      <c r="B10" s="9" t="s">
-        <v>4</v>
+        <v>6</v>
+      </c>
+      <c r="B10" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="C10" s="8" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A11" s="10" t="s">
-        <v>29</v>
+        <v>7</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>0</v>
+        <v>33</v>
+      </c>
+      <c r="C11" s="8" t="s">
+        <v>34</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A12" s="10" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="B12" s="8" t="s">
         <v>5</v>
       </c>
+      <c r="C12" s="8" t="s">
+        <v>36</v>
+      </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A13" s="10" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A14" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="B14" s="8" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A15" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="B15" s="8" t="s">
-        <v>21</v>
-      </c>
+        <v>15</v>
+      </c>
+      <c r="C13" s="8" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A17" s="11"/>
+      <c r="B17" s="11"/>
+      <c r="D17" s="3"/>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A18" s="11"/>
+      <c r="B18" s="11"/>
+      <c r="D18" s="3"/>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A19" s="11"/>
@@ -674,35 +730,25 @@
       <c r="D21" s="3"/>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A22" s="11"/>
-      <c r="B22" s="11"/>
       <c r="D22" s="3"/>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A23" s="11"/>
-      <c r="B23" s="11"/>
       <c r="D23" s="3"/>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.2">
       <c r="D24" s="3"/>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="D25" s="3"/>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="D26" s="3"/>
-    </row>
-    <row r="44" spans="3:3" x14ac:dyDescent="0.2">
-      <c r="C44"/>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="C42"/>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A48" s="7"/>
+    </row>
+    <row r="49" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A49" s="7"/>
     </row>
     <row r="50" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A50" s="7"/>
-    </row>
-    <row r="51" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A51" s="7"/>
-    </row>
-    <row r="52" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A52" s="7"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data-raw/SAA.xlsx
+++ b/data-raw/SAA.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10111"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10313"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sebsilas/Downloads/retranslations/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sebsilas/SAA/data-raw/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{715ECFD8-67F5-EA49-8B74-C48B9B7643A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35C48C48-96F5-B14A-AF12-69F6160C16A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="220" yWindow="1260" windowWidth="28800" windowHeight="17540" xr2:uid="{F918617E-B214-614F-96D8-792A3F23E788}"/>
   </bookViews>
@@ -77,9 +77,6 @@
     <t>In this task we’ll ask you to sing back a few notes and melodies that we play to you. It is fine if you think you are not a good singer. Throughout this first singing test, you will probably find some examples easy and others harder, and in general, as this specific singing test progresses, the trials become more challenging. Just always make your best attempt.</t>
   </si>
   <si>
-    <t>Welcome to the Singing Ability Assessment!</t>
-  </si>
-  <si>
     <t>Singing Ability Assessment</t>
   </si>
   <si>
@@ -147,6 +144,9 @@
   </si>
   <si>
     <t>Wie Sie Singen sollten</t>
+  </si>
+  <si>
+    <t>Welcome to the</t>
   </si>
 </sst>
 </file>
@@ -567,97 +567,97 @@
         <v>2</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D1" s="1"/>
       <c r="E1" s="1"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A2" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>14</v>
+        <v>37</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A3" s="8" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B3" s="9" t="s">
         <v>13</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A4" s="8" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B4" s="9" t="s">
         <v>10</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A5" s="8" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B5" s="9" t="s">
         <v>4</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A6" s="8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B6" s="9" t="s">
         <v>12</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A7" s="8" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B7" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="C7" s="9" t="s">
         <v>29</v>
-      </c>
-      <c r="C7" s="9" t="s">
-        <v>30</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A8" s="8" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B8" s="9" t="s">
         <v>11</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A9" s="10" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B9" s="8" t="s">
         <v>0</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.2">
@@ -668,7 +668,7 @@
         <v>3</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.2">
@@ -676,10 +676,10 @@
         <v>7</v>
       </c>
       <c r="B11" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="C11" s="8" t="s">
         <v>33</v>
-      </c>
-      <c r="C11" s="8" t="s">
-        <v>34</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.2">
@@ -690,7 +690,7 @@
         <v>5</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.2">
@@ -698,10 +698,10 @@
         <v>9</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.2">

--- a/data-raw/SAA.xlsx
+++ b/data-raw/SAA.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sebsilas/SAA/data-raw/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35C48C48-96F5-B14A-AF12-69F6160C16A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AAC585F3-6CC5-0841-8129-9CE68AA71739}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="220" yWindow="1260" windowWidth="28800" windowHeight="17540" xr2:uid="{F918617E-B214-614F-96D8-792A3F23E788}"/>
+    <workbookView xWindow="7660" yWindow="500" windowWidth="28800" windowHeight="17540" xr2:uid="{F918617E-B214-614F-96D8-792A3F23E788}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="48">
   <si>
     <t>Play Note and Sing Along</t>
   </si>
@@ -119,9 +119,6 @@
     <t>Sie werden gebeten werden einige Töne nachzuahmen. Bitte singen Sie diese Noten auf der Sylbe "daah" nach, so wie am Anfang des Names "David".</t>
   </si>
   <si>
-    <t xml:space="preserve"> Try to produce notes that are as stable as possible, without vibrato. That is, try not to wobble your notes. The computer can analyse a “straight” sound best. </t>
-  </si>
-  <si>
     <t>Versuchen Sie Töne zu produzieren, die so stabil wie möglich sind, ohne Vibrato. Das bedeutet, versuchen Sie Ihre Töne nicht flattern zu lassen. Der Computer can einen "klaren" Ton besser analysieren.</t>
   </si>
   <si>
@@ -147,6 +144,39 @@
   </si>
   <si>
     <t>Welcome to the</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Try to produce notes that are as stable as possible, without vibrato. That is, try not to wobble your notes. The computer can analyse a “straight” sound best. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">You can have up to </t>
+  </si>
+  <si>
+    <t>You will have</t>
+  </si>
+  <si>
+    <t>goes to get the melody as best you can.</t>
+  </si>
+  <si>
+    <t>SAA_instructions_5.1</t>
+  </si>
+  <si>
+    <t>SAA_instructions_5.1.forced</t>
+  </si>
+  <si>
+    <t>SAA_instructions_5.2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">goes to get the melody as best you can. </t>
+  </si>
+  <si>
+    <t>SAA_instructions_5.2.forced</t>
+  </si>
+  <si>
+    <t>SAA_instructions_5.3.multiple</t>
+  </si>
+  <si>
+    <t>We encourage you to use as many attempts as you need. It is interesting for us to see improvement over attempts.</t>
   </si>
 </sst>
 </file>
@@ -202,12 +232,18 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor rgb="FFFFFFFF"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -222,7 +258,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -235,6 +271,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -549,7 +586,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5BF35A9C-231E-5348-9328-9A574E33D2C7}">
-  <dimension ref="A1:E50"/>
+  <dimension ref="A1:E55"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="35.1640625" style="2" customWidth="1"/>
@@ -577,7 +614,7 @@
         <v>15</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C2" s="6" t="s">
         <v>24</v>
@@ -613,7 +650,7 @@
         <v>4</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.2">
@@ -632,10 +669,10 @@
         <v>20</v>
       </c>
       <c r="B7" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="C7" s="9" t="s">
         <v>28</v>
-      </c>
-      <c r="C7" s="9" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.2">
@@ -646,109 +683,154 @@
         <v>11</v>
       </c>
       <c r="C8" s="9" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A9" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="B9" s="12" t="s">
+        <v>38</v>
+      </c>
+      <c r="C9" s="9"/>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A10" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="B10" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="C10" s="9"/>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A11" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="B11" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="C11" s="9"/>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A12" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="B12" s="12" t="s">
+        <v>44</v>
+      </c>
+      <c r="C12" s="9"/>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A13" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="B13" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="C13" s="9"/>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A14" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="B14" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="C14" s="8" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A9" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="B9" s="8" t="s">
-        <v>0</v>
-      </c>
-      <c r="C9" s="8" t="s">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A15" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="B15" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="C15" s="8" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A16" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="B16" s="8" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A10" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="B10" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="C10" s="8" t="s">
+      <c r="C16" s="8" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A17" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="B17" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="C17" s="8" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A11" s="10" t="s">
-        <v>7</v>
-      </c>
-      <c r="B11" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="C11" s="8" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A12" s="10" t="s">
-        <v>8</v>
-      </c>
-      <c r="B12" s="8" t="s">
-        <v>5</v>
-      </c>
-      <c r="C12" s="8" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A13" s="10" t="s">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A18" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="B13" s="8" t="s">
+      <c r="B18" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="C13" s="8" t="s">
+      <c r="C18" s="8" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A17" s="11"/>
-      <c r="B17" s="11"/>
-      <c r="D17" s="3"/>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A18" s="11"/>
-      <c r="B18" s="11"/>
-      <c r="D18" s="3"/>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A19" s="11"/>
-      <c r="B19" s="11"/>
-      <c r="D19" s="3"/>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A20" s="11"/>
-      <c r="B20" s="11"/>
-      <c r="D20" s="3"/>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A21" s="11"/>
-      <c r="B21" s="11"/>
-      <c r="D21" s="3"/>
-    </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A22" s="11"/>
+      <c r="B22" s="11"/>
       <c r="D22" s="3"/>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A23" s="11"/>
+      <c r="B23" s="11"/>
       <c r="D23" s="3"/>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A24" s="11"/>
+      <c r="B24" s="11"/>
       <c r="D24" s="3"/>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="C42"/>
-    </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A48" s="7"/>
-    </row>
-    <row r="49" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A49" s="7"/>
-    </row>
-    <row r="50" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A50" s="7"/>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A25" s="11"/>
+      <c r="B25" s="11"/>
+      <c r="D25" s="3"/>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A26" s="11"/>
+      <c r="B26" s="11"/>
+      <c r="D26" s="3"/>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="D27" s="3"/>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="D28" s="3"/>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="D29" s="3"/>
+    </row>
+    <row r="47" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="C47"/>
+    </row>
+    <row r="53" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A53" s="7"/>
+    </row>
+    <row r="54" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A54" s="7"/>
+    </row>
+    <row r="55" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A55" s="7"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data-raw/SAA.xlsx
+++ b/data-raw/SAA.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sebsilas/SAA/data-raw/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AAC585F3-6CC5-0841-8129-9CE68AA71739}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5BE13333-7B56-534A-8119-8C8DA5E7C373}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7660" yWindow="500" windowWidth="28800" windowHeight="17540" xr2:uid="{F918617E-B214-614F-96D8-792A3F23E788}"/>
+    <workbookView xWindow="13620" yWindow="500" windowWidth="28800" windowHeight="17540" xr2:uid="{F918617E-B214-614F-96D8-792A3F23E788}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -167,16 +167,16 @@
     <t>SAA_instructions_5.2</t>
   </si>
   <si>
-    <t xml:space="preserve">goes to get the melody as best you can. </t>
-  </si>
-  <si>
-    <t>SAA_instructions_5.2.forced</t>
-  </si>
-  <si>
-    <t>SAA_instructions_5.3.multiple</t>
-  </si>
-  <si>
     <t>We encourage you to use as many attempts as you need. It is interesting for us to see improvement over attempts.</t>
+  </si>
+  <si>
+    <t>SAA_instructions_5.2.singular</t>
+  </si>
+  <si>
+    <t xml:space="preserve">go to get the melody as best you can. </t>
+  </si>
+  <si>
+    <t>SAA_instructions_5.3</t>
   </si>
 </sst>
 </file>
@@ -718,16 +718,16 @@
         <v>45</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="C12" s="9"/>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A13" s="7" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="C13" s="9"/>
     </row>
